--- a/data/ams_weekly_data/Nexlev/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week14.xlsx
@@ -8043,7 +8043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8205,19 +8205,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2934</v>
+        <v>1855</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>2526.28</v>
+        <v>1597.572040190975</v>
       </c>
       <c r="G5" t="n">
-        <v>7835.59</v>
+        <v>4955.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -8229,28 +8229,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5014.333333333333</v>
+        <v>1079</v>
       </c>
       <c r="E6" t="n">
-        <v>105.6666666666667</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>2325.94</v>
+        <v>928.7079598090254</v>
       </c>
       <c r="G6" t="n">
-        <v>5294.916666666667</v>
+        <v>2880.51</v>
       </c>
       <c r="H6" t="n">
-        <v>2.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8267,23 +8267,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5014.333333333333</v>
+        <v>5697</v>
       </c>
       <c r="E7" t="n">
-        <v>105.6666666666667</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>2325.94</v>
+        <v>2642.370923886117</v>
       </c>
       <c r="G7" t="n">
-        <v>5294.916666666667</v>
+        <v>6015.26</v>
       </c>
       <c r="H7" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8300,23 +8300,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5014.333333333333</v>
+        <v>2367</v>
       </c>
       <c r="E8" t="n">
-        <v>105.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>2325.94</v>
+        <v>1097.821423251861</v>
       </c>
       <c r="G8" t="n">
-        <v>5294.916666666667</v>
+        <v>2499.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8328,28 +8328,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20575.66666666667</v>
+        <v>6980</v>
       </c>
       <c r="E9" t="n">
-        <v>27.33333333333333</v>
+        <v>147</v>
       </c>
       <c r="F9" t="n">
-        <v>345.7966666666667</v>
+        <v>3237.627652862022</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7370.34</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20575.66666666667</v>
+        <v>20576</v>
       </c>
       <c r="E10" t="n">
-        <v>27.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>345.7966666666667</v>
@@ -8399,14 +8399,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20575.66666666667</v>
+        <v>20576</v>
       </c>
       <c r="E11" t="n">
-        <v>27.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>345.7966666666667</v>
@@ -8427,28 +8427,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48668.66666666666</v>
+        <v>20576</v>
       </c>
       <c r="E12" t="n">
-        <v>294.6666666666667</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>6231.676666666667</v>
+        <v>345.7966666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>25385.61</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8465,23 +8465,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48668.66666666666</v>
+        <v>49762</v>
       </c>
       <c r="E13" t="n">
-        <v>294.6666666666667</v>
+        <v>301</v>
       </c>
       <c r="F13" t="n">
-        <v>6231.676666666667</v>
+        <v>6370.51617594796</v>
       </c>
       <c r="G13" t="n">
-        <v>25385.61</v>
+        <v>25956.87987047414</v>
       </c>
       <c r="H13" t="n">
-        <v>8.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8498,23 +8498,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48668.66666666666</v>
+        <v>6492</v>
       </c>
       <c r="E14" t="n">
-        <v>294.6666666666667</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
-        <v>6231.676666666667</v>
+        <v>824.7937229372615</v>
       </c>
       <c r="G14" t="n">
-        <v>25385.61</v>
+        <v>3393.701156892096</v>
       </c>
       <c r="H14" t="n">
-        <v>8.333333333333334</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8526,28 +8526,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2511.5</v>
+        <v>52745</v>
       </c>
       <c r="E15" t="n">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="F15" t="n">
-        <v>1563.515</v>
+        <v>6749.577925931612</v>
       </c>
       <c r="G15" t="n">
-        <v>2665.71</v>
+        <v>27516.56960098257</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8559,28 +8559,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2511.5</v>
+        <v>35824</v>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="F16" t="n">
-        <v>1563.515</v>
+        <v>4599.85461585482</v>
       </c>
       <c r="G16" t="n">
-        <v>2665.71</v>
+        <v>18671.30528637957</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8592,25 +8592,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3349</v>
+        <v>700</v>
       </c>
       <c r="E17" t="n">
-        <v>85.5</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>597.4299999999999</v>
+        <v>88.96905637578931</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>366.0726084030603</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -8625,25 +8625,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3349</v>
+        <v>483</v>
       </c>
       <c r="E18" t="n">
-        <v>85.5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>597.4299999999999</v>
+        <v>61.31850295255723</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>252.3014768685551</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -8658,28 +8658,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27874</v>
+        <v>5023</v>
       </c>
       <c r="E19" t="n">
-        <v>533</v>
+        <v>190</v>
       </c>
       <c r="F19" t="n">
-        <v>7605.78</v>
+        <v>3127.03</v>
       </c>
       <c r="G19" t="n">
-        <v>40260.18</v>
+        <v>5331.42</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8691,28 +8691,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1493</v>
+        <v>3349</v>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>313.76</v>
+        <v>597.4299999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>3807.62</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8724,28 +8724,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1493</v>
+        <v>3349</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F21" t="n">
-        <v>313.76</v>
+        <v>597.4299999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>3807.62</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8757,28 +8757,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13244</v>
+        <v>20854</v>
       </c>
       <c r="E22" t="n">
-        <v>543</v>
+        <v>399</v>
       </c>
       <c r="F22" t="n">
-        <v>6240.99</v>
+        <v>5686.027542020428</v>
       </c>
       <c r="G22" t="n">
-        <v>27163.59</v>
+        <v>30094.07</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8790,28 +8790,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20509</v>
+        <v>7020</v>
       </c>
       <c r="E23" t="n">
-        <v>33.5</v>
+        <v>134</v>
       </c>
       <c r="F23" t="n">
-        <v>529.71</v>
+        <v>1919.752457979572</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>10166.11</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8823,30 +8823,261 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2986</v>
+      </c>
+      <c r="E24" t="n">
+        <v>140</v>
+      </c>
+      <c r="F24" t="n">
+        <v>627.52</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7615.24</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2933</v>
+      </c>
+      <c r="E25" t="n">
+        <v>120</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1382.040352817871</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6015.26</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1513</v>
+      </c>
+      <c r="E26" t="n">
+        <v>62</v>
+      </c>
+      <c r="F26" t="n">
+        <v>713.0238810849376</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3103.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7435</v>
+      </c>
+      <c r="E27" t="n">
+        <v>305</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3503.776927493752</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15250.01</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1198</v>
+      </c>
+      <c r="E28" t="n">
+        <v>49</v>
+      </c>
+      <c r="F28" t="n">
+        <v>564.4592416613563</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2456.78</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0F678L8YT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>165</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>77.68959694208313</v>
+      </c>
+      <c r="G29" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20509</v>
+      </c>
+      <c r="E30" t="n">
+        <v>34</v>
+      </c>
+      <c r="F30" t="n">
+        <v>529.71</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D31" t="n">
         <v>20509</v>
       </c>
-      <c r="E24" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E31" t="n">
+        <v>34</v>
+      </c>
+      <c r="F31" t="n">
         <v>529.71</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week14.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
